--- a/Excel/data.xlsx
+++ b/Excel/data.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dimit\Documents\DataAnalytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E665A5-A5C3-4159-B862-5E9DCA9FBB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA1C6F1-A7B4-4B83-B181-445475D13C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17840" yWindow="2090" windowWidth="20820" windowHeight="15200" xr2:uid="{99E1D9B9-B149-4022-82A1-78AB0C3DED42}"/>
+    <workbookView xWindow="18560" yWindow="3910" windowWidth="18430" windowHeight="12610" activeTab="1" xr2:uid="{99E1D9B9-B149-4022-82A1-78AB0C3DED42}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="dataset-1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="dataset-2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Dataset</t>
   </si>
@@ -121,6 +126,36 @@
   </si>
   <si>
     <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>Track</t>
+  </si>
+  <si>
+    <t>AppDev</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>PST</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Score</t>
   </si>
 </sst>
 </file>
@@ -162,8 +197,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -179,6 +222,188 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dimitri Nji" refreshedDate="46108.566631712965" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{BCB7D08C-0C2E-4C7A-8DA1-B65C51FCF4E4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A2:D12" sheet="dataset-2"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Student" numFmtId="0">
+      <sharedItems count="10">
+        <s v="Student 1"/>
+        <s v="Student 2"/>
+        <s v="Student 3"/>
+        <s v="Student 4"/>
+        <s v="Student 5"/>
+        <s v="Student 6"/>
+        <s v="Student 7"/>
+        <s v="Student 8"/>
+        <s v="Student 9"/>
+        <s v="Student 10"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Score" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="65" maxValue="95"/>
+    </cacheField>
+    <cacheField name="Track" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Time Zone" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <x v="0"/>
+    <n v="65"/>
+    <s v="AppDev"/>
+    <s v="EST"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="70"/>
+    <s v="AppDev"/>
+    <s v="CST"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="75"/>
+    <s v="Data Analytics"/>
+    <s v="PST"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="80"/>
+    <s v="Data Analytics"/>
+    <s v="EST"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="85"/>
+    <s v="AppDev"/>
+    <s v="EST"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="90"/>
+    <s v="AppDev"/>
+    <s v="PST"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="75"/>
+    <s v="AppDev"/>
+    <s v="EST"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="80"/>
+    <s v="Data Analytics"/>
+    <s v="PST"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="95"/>
+    <s v="Data Analytics"/>
+    <s v="EST"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="70"/>
+    <s v="AppDev"/>
+    <s v="CST"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{958E293F-9C5D-49CD-841A-470E18CC220E}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Score" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -655,4 +880,292 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9983F7A3-A347-4941-B74E-7CDCE3FDBC9D}">
+  <dimension ref="A3:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4">
+        <v>785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06617C8-A1DA-4AC4-B901-2FBA296A3A57}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="1"/>
+    <col min="8" max="8" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>